--- a/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20261015.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20261015.xlsx
@@ -997,17 +997,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>162,062,180</t>
+          <t>23,901,768</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1019,17 +1019,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>23,901,768</t>
+          <t>162,062,180</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
